--- a/data/trans_dic/IP16B_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16B_2023-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores vacunados de la triple vírica</t>
+          <t>Menores vacunados de la triple vírica (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>95,47; 99,38</t>
+          <t>95,73; 99,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>96,07; 99,65</t>
+          <t>95,93; 99,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96,96; 99,39</t>
+          <t>97,03; 99,38</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>97,0; 99,6</t>
+          <t>97,02; 99,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>95,43; 98,68</t>
+          <t>95,48; 98,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96,89; 98,9</t>
+          <t>96,76; 98,9</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>95,13; 99,14</t>
+          <t>94,91; 99,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>95,72; 99,04</t>
+          <t>95,58; 99,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96,24; 98,82</t>
+          <t>96,11; 98,66</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>96,66; 99,65</t>
+          <t>96,66; 99,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>97,06; 100,0</t>
+          <t>97,05; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97,77; 99,65</t>
+          <t>97,63; 99,73</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>97,5; 99,04</t>
+          <t>97,54; 99,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>97,3; 98,86</t>
+          <t>97,35; 98,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97,72; 98,83</t>
+          <t>97,66; 98,78</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores vacunados de la triple vírica (tasa de respuesta: 98,91%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>113099</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>133176</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>246276</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>110094; 114612</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>129435; 134490</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>242498; 248385</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>187579</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>245498</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>433077</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>184048; 189227</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>240289; 248435</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>427075; 436521</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>183641</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>178782</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>362423</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>178396; 186344</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>174680; 180978</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>356300; 365761</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>163334</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>179725</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>343059</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>159851; 164777</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>175891; 181238</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>338405; 345665</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>647654</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>737181</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1384834</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>641840; 651686</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>730668; 741879</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1375720; 1391436</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16B_2023-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>95,73; 99,66</t>
+          <t>95,26; 99,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>95,93; 99,67</t>
+          <t>95,56; 99,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97,03; 99,38</t>
+          <t>96,93; 99,41</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>97,02; 99,75</t>
+          <t>97,1; 99,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>95,48; 98,72</t>
+          <t>95,62; 98,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96,76; 98,9</t>
+          <t>96,96; 98,94</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>94,91; 99,14</t>
+          <t>95,33; 99,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>95,58; 99,02</t>
+          <t>95,64; 99,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96,11; 98,66</t>
+          <t>96,3; 98,77</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>96,66; 99,64</t>
+          <t>96,62; 99,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>97,05; 100,0</t>
+          <t>96,89; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97,63; 99,73</t>
+          <t>97,72; 99,73</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>97,54; 99,04</t>
+          <t>97,54; 99,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>97,35; 98,84</t>
+          <t>97,28; 98,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97,66; 98,78</t>
+          <t>97,68; 98,79</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>110094; 114612</t>
+          <t>109553; 114283</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>129435; 134490</t>
+          <t>128944; 134478</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>242498; 248385</t>
+          <t>242268; 248458</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>184048; 189227</t>
+          <t>184209; 188940</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>240289; 248435</t>
+          <t>240637; 248538</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>427075; 436521</t>
+          <t>427943; 436660</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>178396; 186344</t>
+          <t>179169; 186460</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>174680; 180978</t>
+          <t>174800; 180936</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>356300; 365761</t>
+          <t>357018; 366144</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>159851; 164777</t>
+          <t>159776; 164783</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>175891; 181238</t>
+          <t>175607; 181238</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>338405; 345665</t>
+          <t>338711; 345668</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>641840; 651686</t>
+          <t>641857; 651919</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>730668; 741879</t>
+          <t>730188; 741701</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1375720; 1391436</t>
+          <t>1375972; 1391602</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16B_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16B_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>95,26; 99,37</t>
+          <t>96,41; 99,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>95,56; 99,66</t>
+          <t>96,14; 99,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96,93; 99,41</t>
+          <t>97,36; 99,47</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>97,1; 99,6</t>
+          <t>95,55; 98,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>95,62; 98,76</t>
+          <t>97,93; 99,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96,96; 98,94</t>
+          <t>97,28; 99,06</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>95,33; 99,2</t>
+          <t>95,93; 99,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>95,64; 99,0</t>
+          <t>94,28; 98,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96,3; 98,77</t>
+          <t>95,79; 98,66</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>96,62; 99,64</t>
+          <t>96,65; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>96,89; 100,0</t>
+          <t>96,89; 99,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97,72; 99,73</t>
+          <t>97,82; 99,69</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>97,54; 99,07</t>
+          <t>97,42; 98,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>97,28; 98,82</t>
+          <t>97,54; 99,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97,68; 98,79</t>
+          <t>97,85; 98,89</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>189</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>113099</t>
+          <t>120165</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>133176</t>
+          <t>117541</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>246276</t>
+          <t>237705</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>109553; 114283</t>
+          <t>117251; 121238</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>128944; 134478</t>
+          <t>114583; 118652</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>242268; 248458</t>
+          <t>234441; 239514</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>275</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>187579</t>
+          <t>228278</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>245498</t>
+          <t>182023</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>433077</t>
+          <t>410301</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>184209; 188940</t>
+          <t>223264; 230853</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>240637; 248538</t>
+          <t>179741; 183163</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>427943; 436660</t>
+          <t>405866; 413273</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>217</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>183641</t>
+          <t>162573</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>178782</t>
+          <t>150273</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>362423</t>
+          <t>312846</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>179169; 186460</t>
+          <t>159168; 164477</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>174800; 180936</t>
+          <t>145716; 152775</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>357018; 366144</t>
+          <t>307004; 316203</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>233</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>163334</t>
+          <t>167951</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>179725</t>
+          <t>162583</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343059</t>
+          <t>330535</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>159776; 164783</t>
+          <t>163699; 169376</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>175607; 181238</t>
+          <t>159373; 163983</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>338711; 345668</t>
+          <t>326589; 332820</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>914</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>647654</t>
+          <t>678968</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>737181</t>
+          <t>612419</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1384834</t>
+          <t>1291387</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>641857; 651919</t>
+          <t>672766; 683176</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>730188; 741701</t>
+          <t>606483; 616045</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1375972; 1391602</t>
+          <t>1284136; 1297813</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16B_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16B_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores vacunados de la triple vírica (tasa de respuesta: 98,91%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>98,8%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>98,62%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>96,41; 99,68</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>96,14; 99,56</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>97,36; 99,47</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>97,7%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>95,55; 98,8</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>97,93; 99,79</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>97,28; 99,06</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>97,98%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>97,23%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>97,62%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>95,93; 99,13</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>94,28; 98,84</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>95,79; 98,66</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>99,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>96,65; 100,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>96,89; 99,69</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>97,82; 99,69</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>98,32%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>98,49%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>97,42; 98,93</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>97,54; 99,08</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>97,85; 98,89</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.9880324062592007</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9862275241078245</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9871391053609688</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>120165</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>117541</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>237705</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.9640662801291831</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.9614152364669518</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.9735843824599126</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>117251; 121238</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114583; 118652</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>234441; 239514</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9968491171132043</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9955513610989819</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9946515871449066</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9769834260920977</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9916862688604895</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.983451917701494</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>228278</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>182023</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>410301</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.9555242452524888</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.9792530884805878</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.9728210553361066</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>223264; 230853</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>179741; 183163</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>405866; 413273</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9880028487138988</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9978961015979697</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9905757053778685</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.9797837680178644</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9722594733535116</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.9761550482902206</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>162573</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>150273</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>312846</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.9592652665831142</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.942772990860024</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.9579268625810704</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>159168; 164477</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>145716; 152775</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>307004; 316203</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.9912602801826681</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9884424382604958</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9866312663032772</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.9915896070335449</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9883792802460545</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.990007912583353</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>167951</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>162583</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>330535</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.9664830982370312</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.9688630964559888</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.9781882487798783</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>163699; 169376</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>159373; 163983</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>326589; 332820</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9968896482705663</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9968515863091105</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1855</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.9831845533667184</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.984936061310289</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.9840144001567201</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>678968</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>612419</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1291387</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.9742045800160193</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.9753881255881106</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.9784892211521231</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>672766; 683176</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>606483; 616045</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1284136; 1297813</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.989278034787609</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.9907666452958105</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.9889110041734674</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores vacunados de la triple vírica (tasa de respuesta: 98,91%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>164</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>189</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>120165</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>117541</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>237705</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>117251</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>114583</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>234441</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>121238</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>118652</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>239514</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>327</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>275</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>228278</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>182023</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>410301</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>223264</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>179741</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>405866</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>230853</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>183163</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>413273</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>214</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>217</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>162573</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>150273</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>312846</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>159168</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>145716</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>307004</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>164477</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>152775</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>316203</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>236</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>233</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>167951</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>162583</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>330535</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>163699</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>159373</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>326589</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>169376</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>163983</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>332820</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>941</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>914</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>678968</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>612419</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1291387</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>672766</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>606483</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1284136</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>683176</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>616045</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1297813</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>